--- a/Utils/Deepam_Dataset.xlsx
+++ b/Utils/Deepam_Dataset.xlsx
@@ -1592,7 +1592,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="1">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D2" s="2">
         <v>0.416666666666667</v>
